--- a/public/plantilla-cal-resultados.xlsx
+++ b/public/plantilla-cal-resultados.xlsx
@@ -12393,7 +12393,7 @@
       </c>
       <c r="H28" s="32" t="n"/>
       <c r="I28" s="148">
-        <f>IFERROR(_xludf.MINIFS(I15:I26,F15:F26,28),"")</f>
+        <f>IF(D28=0,"",1000000-SUMPRODUCT(MAX((F15:F26=28)*(I15:I26&lt;&gt;"")*(1000000-I15:I26))))</f>
         <v/>
       </c>
       <c r="J28" s="32" t="n"/>
